--- a/eMudhra-response-workbook.xlsx
+++ b/eMudhra-response-workbook.xlsx
@@ -157,7 +157,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Optional: the pack's original tier, for traceability.</t>
+          <t xml:space="preserve">Optional: the version 1 tier, for records created before 26 Oct.</t>
         </r>
       </text>
     </comment>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">eMudhra response workbook</t>
   </si>
   <si>
-    <t xml:space="preserve">Version 0.1.0 · 26 October 2026 · Proposed — no decisions have been taken and no team data has been entered. Companion to REVIEW.md and playbooks/ in the eMudhraResponse repository.</t>
+    <t xml:space="preserve">Version 0.1.0 · 26 October 2026 · Proposed — no decisions have been taken and no team data has been entered. Companion to ACTION_PLAN.md, RISK_TIERS.md, COMPLETION_TRACKER.md and playbooks/ in the eMudhraResponse repository.</t>
   </si>
   <si>
     <t xml:space="preserve">Purpose</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">Where to keep it</t>
   </si>
   <si>
-    <t xml:space="preserve">Keep the populated copy in the internal incident or change system. Do not commit populated inventories, hostnames or logs to a public repository (pack rule).</t>
+    <t xml:space="preserve">Keep the populated copy in the internal incident or change system. Do not commit populated inventories, hostnames or logs to a public repository (Completion tracker rule).</t>
   </si>
   <si>
     <t xml:space="preserve">Who fills what</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">Priority</t>
   </si>
   <si>
-    <t xml:space="preserve">Priority = Impact (H/M/L, using the pack's tier definitions) × Verifier susceptibility (A–D or Unknown). See Lists!T1 for the matrix and key. Proposed in REVIEW.md §3.3; adoption is decision D-01. Indicative windows (decision D-03, not approved): P1 contain 72 h / close 7 days; P2 14 days; P3 30 days; P4 normal cycle.</t>
+    <t xml:space="preserve">Priority = Impact (H/M/L, as defined in RISK_TIERS.md §2) × Verifier susceptibility (A–D or Unknown). See Lists!T1 for the matrix and key. Defined in RISK_TIERS.md §4; approval is decision D-01. Indicative windows (decision D-03, not approved): P1 contain 72 h / close 7 days; P2 14 days; P3 30 days; P4 normal cycle.</t>
   </si>
   <si>
     <t xml:space="preserve">eMudhra response — dashboard</t>
@@ -599,12 +599,12 @@
     <t xml:space="preserve">Tier 2 currently mixes vendor-protected browsers with exposed API clients</t>
   </si>
   <si>
-    <t xml:space="preserve">1) Keep the pack's four tiers as they are
+    <t xml:space="preserve">1) Keep the version 1 four tiers
 2) Impact × verifier susceptibility matrix, keeping tier labels for impact
 3) Separate lists per platform team</t>
   </si>
   <si>
-    <t xml:space="preserve">Option 2 (REVIEW §3.3). Existing tier labels still map to impact</t>
+    <t xml:space="preserve">Option 2, as defined in RISK_TIERS.md. Version 1 tiers map to impact</t>
   </si>
   <si>
     <t xml:space="preserve">Incident lead</t>
@@ -616,7 +616,7 @@
     <t xml:space="preserve">Open</t>
   </si>
   <si>
-    <t xml:space="preserve">REVIEW §3; Lists!T1</t>
+    <t xml:space="preserve">RISK_TIERS §2–4; Lists!T1</t>
   </si>
   <si>
     <t xml:space="preserve">D-02</t>
@@ -639,7 +639,7 @@
     <t xml:space="preserve">Head of EUC</t>
   </si>
   <si>
-    <t xml:space="preserve">REVIEW §4; PB-01; Browser &amp; desktop sheet</t>
+    <t xml:space="preserve">ACTION_PLAN §5; PB-01; Browser &amp; desktop sheet</t>
   </si>
   <si>
     <t xml:space="preserve">D-03</t>
@@ -648,7 +648,7 @@
     <t xml:space="preserve">Set indicative target windows per priority</t>
   </si>
   <si>
-    <t xml:space="preserve">The pack sets no SLA, so overdue work can't be distinguished from on-track</t>
+    <t xml:space="preserve">Version 1 set no target windows, so overdue work couldn't be distinguished from on-track</t>
   </si>
   <si>
     <t xml:space="preserve">1) No windows; agree per service
@@ -665,7 +665,7 @@
     <t xml:space="preserve">Risk committee</t>
   </si>
   <si>
-    <t xml:space="preserve">REVIEW §3.3</t>
+    <t xml:space="preserve">RISK_TIERS §4; ACTION_PLAN §10</t>
   </si>
   <si>
     <t xml:space="preserve">D-04</t>
@@ -791,10 +791,10 @@
 3) Hard deadline with shutdown</t>
   </si>
   <si>
-    <t xml:space="preserve">Option 2; propose cut-off of 30 Nov 2026 for P1/P2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVIEW §5.3; PB-11; Exceptions</t>
+    <t xml:space="preserve">Option 2; cut-off 25 Nov 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTION_PLAN §6; PB-11; Exceptions</t>
   </si>
   <si>
     <t xml:space="preserve">D-10</t>
@@ -826,7 +826,7 @@
     <t xml:space="preserve">Regulatory and notification stance</t>
   </si>
   <si>
-    <t xml:space="preserve">HK legal entity with UK affiliates; obligations differ by regulator</t>
+    <t xml:space="preserve">Obligations differ by jurisdiction and regulator</t>
   </si>
   <si>
     <t xml:space="preserve">1) No position
@@ -834,7 +834,7 @@
 3) Precautionary notification</t>
   </si>
   <si>
-    <t xml:space="preserve">Option 2; Legal to confirm the applicable HK and UK regulators and triggers</t>
+    <t xml:space="preserve">Option 2; Legal confirms regulators per jurisdiction</t>
   </si>
   <si>
     <t xml:space="preserve">General Counsel</t>
@@ -857,7 +857,7 @@
 3) Daily executive updates</t>
   </si>
   <si>
-    <t xml:space="preserve">Option 2; daily only for P1 open items, blockers and outages (pack rule)</t>
+    <t xml:space="preserve">Option 2; daily only for P1 open items, blockers and outages</t>
   </si>
   <si>
     <t xml:space="preserve">D-13</t>
@@ -897,7 +897,7 @@
     <t xml:space="preserve">Option 2; remaining P3/P4 move to business-as-usual vulnerability management</t>
   </si>
   <si>
-    <t xml:space="preserve">REVIEW §8</t>
+    <t xml:space="preserve">ACTION_PLAN §2</t>
   </si>
   <si>
     <t xml:space="preserve">D-15</t>
@@ -967,7 +967,7 @@
     <t xml:space="preserve">2. Verifier susceptibility</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Pack tier (1–4)</t>
+    <t xml:space="preserve">Version 1 tier (1–4)</t>
   </si>
   <si>
     <t xml:space="preserve">2. Rationale</t>
@@ -1597,7 +1597,7 @@
     <t xml:space="preserve">Apple block; Sectigo revokes eight AAA cross-certificates; Android protection via Google Play services</t>
   </si>
   <si>
-    <t xml:space="preserve">BleepingComputer; Technobezz; pack</t>
+    <t xml:space="preserve">BleepingComputer; Technobezz; Sectigo advisory</t>
   </si>
   <si>
     <t xml:space="preserve">Go 1.27.3 and 1.26.10 published (reject chains with the eight keys; rebuild required)</t>
@@ -1669,7 +1669,7 @@
     <t xml:space="preserve">Oracle JDK advisory updated: action needed even on listed builds</t>
   </si>
   <si>
-    <t xml:space="preserve">Per pack</t>
+    <t xml:space="preserve">Vendor advisory</t>
   </si>
   <si>
     <t xml:space="preserve">ops.java/emudhra</t>

--- a/eMudhra-response-workbook.xlsx
+++ b/eMudhra-response-workbook.xlsx
@@ -318,12 +318,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="605">
   <si>
     <t xml:space="preserve">eMudhra response workbook</t>
   </si>
   <si>
-    <t xml:space="preserve">Version 0.1.0 · 26 October 2026 · Proposed — no decisions have been taken and no team data has been entered. Companion to ACTION_PLAN.md, RISK_TIERS.md, COMPLETION_TRACKER.md and playbooks/ in the eMudhraResponse repository.</t>
+    <t xml:space="preserve">Version 2.2 · 27 October 2026 · Proposed — no decisions have been taken and no team data has been entered. Companion to ACTION_PLAN.md, RISK_TIERS.md, COMPLETION_TRACKER.md and playbooks/ in the eMudhraResponse repository.</t>
   </si>
   <si>
     <t xml:space="preserve">Purpose</t>
@@ -1228,406 +1228,424 @@
     <t xml:space="preserve">Windows 11 + Edge</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft block</t>
+    <t xml:space="preserve">Windows Disallowed list (20 Oct); Edge CRLSet (reported); seven certificates removed from the Windows trust list (26 Oct) and Edge trust list (27 Oct)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 / 26 / 27 Oct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows, disconnected or locked down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Out-of-band trust-list update installed from the Microsoft Update Catalog (reported KB5134130/33/34)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 Oct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows + Firefox ESR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OneCRL via Remote Settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 Oct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">macOS + Safari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 Oct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">macOS + Chrome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRLSet; Chrome Root Store change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VDI image (name)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per browser above; image refresh required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChromeOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Android with Google Play services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equivalent block via Google Play services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c. 19 Oct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Android without Google Play services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not covered by Play services delivery — OEM update needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treat as long tail (PB-11) until the OEM confirms a fix.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iOS / iPadOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proviso: covers the browser and OS trust store only. Not covered: macOS /usr/bin/curl and other CLI tools, Java, Python, Node and Go apps, Electron apps, VPN/ZTNA and management agents, developer toolchains — record those on the Long tail sheet. Vendor dates are from press reports of vendor statements; confirm on the Facts sheet. Coverage threshold is Lists!U16 (assumption pending D-02).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System / product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovered via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor / supplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Susceptibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor ref / date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interim control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exception ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EX-LT-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building management system cloud connector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT / IoT / facilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egress telemetry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facilities IT (example)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor X (example)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ticket 0000, 24 Oct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egress restricted to vendor endpoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXC-EX-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor ETA mid-November</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endpoint / hostname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Issuer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Affected by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replacement CA / action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planned date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EX-AV-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">partner-api.example.net</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">External</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration owner (example)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emSign ECC CA - G3 (example)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emSign ECC Root CA - G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partner to replace certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time-boxed exception EXC-EX-2 if it breaks first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linked record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compensating control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residual risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requested by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approved date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expiry / review date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days to expiry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor fix not available until mid-November</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egress restricted to two vendor endpoints; alert on any other destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISO delegate (example)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retention starts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Searched from</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Searched to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap to window start (days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Query reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disposition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binaries signed under the two affected code-signing intermediates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDR file-signature telemetry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upstream certificates issued by the six TLS intermediates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLS-inspection / SWG logs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same issuers in passive TLS (TLS 1.2 and older only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDR / Zeek x509.log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peer certificate details on P1 integrations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application TLS logs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certificates for our domains chaining to the intermediates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certificate Transparency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unexpected JWKS kid values or SAML signing-certificate changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IdP and API logs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date (2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last checked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 Apr 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eight intermediate keys generated with P-384 private values below 256; recoverable from public data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secondary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Press Journal; BleepingComputer (citing Mozilla)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Six TLS intermediates, two code-signing (reported as trusted by Microsoft); eMudhra says none issued end-entity certificates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSO Online; Free Press Journal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report received; Chrome CRLSet and Firefox OneCRL block (no browser update or restart needed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary (Google)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blog.google; The Hacker News</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple block; Sectigo revokes eight AAA cross-certificates; Android protection via Google Play services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BleepingComputer; Technobezz; Sectigo advisory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go 1.27.3 and 1.26.10 published (reject chains with the eight keys; rebuild required)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified (release); Secondary (content)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proxy.golang.org toolchain index; Rescana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rust webpki-roots 1.0.10 removes emSign ECC Root CA - G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crates.io package contents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18–23 Oct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python certifi 2026.10.18+ removes emSign ECC Root CA - G3; 2026.10.23 keeps only emSign Root CA - G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PyPI package contents</t>
   </si>
   <si>
     <t xml:space="preserve">20 Oct</t>
   </si>
   <si>
-    <t xml:space="preserve">Windows + Firefox ESR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OneCRL via Remote Settings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 Oct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">macOS + Safari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 Oct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">macOS + Chrome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRLSet; Chrome Root Store change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VDI image (name)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per browser above; image refresh required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChromeOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Android with Google Play services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equivalent block via Google Play services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c. 19 Oct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Android without Google Play services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not covered by Play services delivery — OEM update needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treat as long tail (PB-11) until the OEM confirms a fix.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iOS / iPadOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proviso: covers the browser and OS trust store only. Not covered: macOS /usr/bin/curl and other CLI tools, Java, Python, Node and Go apps, Electron apps, VPN/ZTNA and management agents, developer toolchains — record those on the Long tail sheet. Vendor dates are from press reports of vendor statements; confirm on the Facts sheet. Coverage threshold is Lists!U16 (assumption pending D-02).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System / product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discovered via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor / supplier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Susceptibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor ref / date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interim control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exception ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EX-LT-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Building management system cloud connector</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT / IoT / facilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egress telemetry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facilities IT (example)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor X (example)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ticket 0000, 24 Oct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egress restricted to vendor endpoints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXC-EX-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor ETA mid-November</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endpoint / hostname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Issuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Affected by</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Replacement CA / action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planned date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EX-AV-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">partner-api.example.net</t>
-  </si>
-  <si>
-    <t xml:space="preserve">We call</t>
-  </si>
-  <si>
-    <t xml:space="preserve">External</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integration owner (example)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emSign ECC CA - G3 (example)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emSign ECC Root CA - G3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner to replace certificate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time-boxed exception EXC-EX-2 if it breaks first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linked record</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compensating control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residual risk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requested by</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approved date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expiry / review date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days to expiry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor fix not available until mid-November</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egress restricted to two vendor endpoints; alert on any other destination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CISO delegate (example)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retention starts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Searched from</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Searched to</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gap to window start (days)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Query reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disposition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binaries signed under the two affected code-signing intermediates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDR file-signature telemetry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upstream certificates issued by the six TLS intermediates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLS-inspection / SWG logs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same issuers in passive TLS (TLS 1.2 and older only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDR / Zeek x509.log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peer certificate details on P1 integrations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application TLS logs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certificates for our domains chaining to the intermediates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certificate Transparency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unexpected JWKS kid values or SAML signing-certificate changes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IdP and API logs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date (2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Event</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last checked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 Apr 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eight intermediate keys generated with P-384 private values below 256; recoverable from public data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secondary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Press Journal; BleepingComputer (citing Mozilla)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Response lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Six TLS intermediates, two code-signing (reported as trusted by Microsoft); eMudhra says none issued end-entity certificates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSO Online; Free Press Journal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report received; Chrome CRLSet and Firefox OneCRL block (no browser update or restart needed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary (Google)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blog.google; The Hacker News</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple block; Sectigo revokes eight AAA cross-certificates; Android protection via Google Play services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BleepingComputer; Technobezz; Sectigo advisory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go 1.27.3 and 1.26.10 published (reject chains with the eight keys; rebuild required)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verified (release); Secondary (content)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proxy.golang.org toolchain index; Rescana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rust webpki-roots 1.0.10 removes emSign ECC Root CA - G3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crates.io package contents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18–23 Oct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python certifi 2026.10.18+ removes emSign ECC Root CA - G3; 2026.10.23 keeps only emSign Root CA - G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PyPI package contents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Press Journal</t>
+    <t xml:space="preserve">Microsoft updates the Windows Disallowed Certificate Trust List; Edge and WebView2 CRLSet update (reported)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary (Microsoft); CRLSet secondary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSRC blog; Help Net Security</t>
   </si>
   <si>
     <t xml:space="preserve">Ubuntu 24.04 ca-certificates 20260816ubuntu0.24.04.1 blocklists emSign ECC Root CA - G3 (LP #2171507)</t>
@@ -1639,13 +1657,22 @@
     <t xml:space="preserve">20–21 Oct</t>
   </si>
   <si>
-    <t xml:space="preserve">Node.js, Bun, Debian, FreeBSD fixes pending; macOS /usr/bin/curl still accepted chain after Apple block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rescana; lilting.ch; CSO Online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 Oct</t>
+    <t xml:space="preserve">Node.js security releases 22.23.4, 24.22.1 (20 Oct), 26.12.1 (21 Oct); Debian 13 reported patched; Bun and FreeBSD unconfirmed; macOS /usr/bin/curl still accepted chain after Apple block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node releases verified; fix content secondary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nodejs.org release index; Fleet; lilting.ch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 Oct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eMudhra announces exit from the global SSL/TLS certificate business; free replacements via partners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hacker News; CSO Online</t>
   </si>
   <si>
     <t xml:space="preserve">Node.js 22.22.0 built-in roots still include emSign ECC Root CA - G3</t>
@@ -1675,16 +1702,25 @@
     <t xml:space="preserve">ops.java/emudhra</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft out-of-band update removes seven certificates (including an AAA Certificate Services cross-sign) from the Windows trust list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary (Microsoft); KB numbers secondary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSRC blog; NTCompatible</t>
+  </si>
+  <si>
     <t xml:space="preserve">27 Oct</t>
   </si>
   <si>
-    <t xml:space="preserve">Chrome removes emSign ECC Root CA - G3 from Chrome Root Store (~30,000 certificates to migrate, eMudhra estimate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary (Google); Secondary (estimate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blog.google</t>
+    <t xml:space="preserve">Chrome removes emSign ECC Root CA - G3 from Chrome Root Store; Microsoft removes the same seven certificates from the Edge trust list (~30,000 certificates to migrate, eMudhra estimate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary (Google, Microsoft); Secondary (estimate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blog.google; MSRC blog</t>
   </si>
   <si>
     <t xml:space="preserve">Code</t>
@@ -3115,40 +3151,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="M1" s="16" t="s">
         <v>84</v>
@@ -3156,13 +3192,13 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D2" s="21"/>
       <c r="E2" s="21"/>
@@ -3182,13 +3218,13 @@
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="20" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
@@ -3208,13 +3244,13 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D4" s="21"/>
       <c r="E4" s="21"/>
@@ -3234,13 +3270,13 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="21"/>
@@ -3260,13 +3296,13 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D6" s="21"/>
       <c r="E6" s="21"/>
@@ -3286,13 +3322,13 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
@@ -3928,7 +3964,7 @@
     <tabColor rgb="FF1B2A4A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3941,19 +3977,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F1" s="16" t="s">
         <v>277</v>
@@ -3961,299 +3997,323 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E2" s="21" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="C3" s="20" t="s">
         <v>408</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>409</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>405</v>
-      </c>
       <c r="D3" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="E3" s="21" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F3" s="20" t="s">
         <v>410</v>
-      </c>
-      <c r="E3" s="21" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E4" s="21" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E5" s="21" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B8" s="20" t="s">
+        <v>426</v>
+      </c>
+      <c r="C8" s="20" t="s">
         <v>423</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>420</v>
-      </c>
       <c r="D8" s="20" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>293</v>
+        <v>428</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>292</v>
+        <v>429</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>293</v>
+        <v>428</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>405</v>
+        <v>436</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>434</v>
+        <v>296</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>439</v>
+        <v>408</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="20"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="20"/>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>454</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>455</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>456</v>
+      </c>
+      <c r="E17" s="21" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20"/>
@@ -4398,6 +4458,22 @@
       <c r="D35" s="20"/>
       <c r="E35" s="21"/>
       <c r="F35" s="20"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="20"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="20"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="20"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4428,19 +4504,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>252</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4448,16 +4524,16 @@
         <v>177</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4465,50 +4541,50 @@
         <v>246</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4516,84 +4592,84 @@
         <v>231</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4601,16 +4677,16 @@
         <v>139</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4618,84 +4694,84 @@
         <v>190</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4703,33 +4779,33 @@
         <v>197</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -4781,61 +4857,61 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="32" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="D1" s="32" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="E1" s="32" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="F1" s="32" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="G1" s="32" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="H1" s="32" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="I1" s="32" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J1" s="32" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="K1" s="32" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L1" s="32" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="M1" s="32" t="s">
         <v>209</v>
       </c>
       <c r="N1" s="32" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="O1" s="32" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="P1" s="32" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="Q1" s="32" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="R1" s="32" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4855,22 +4931,22 @@
         <v>244</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>270</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>97</v>
@@ -4882,19 +4958,19 @@
         <v>97</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="T2" s="33" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="U2" s="33" t="s">
         <v>242</v>
@@ -4906,10 +4982,10 @@
         <v>227</v>
       </c>
       <c r="X2" s="33" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Y2" s="33" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4920,7 +4996,7 @@
         <v>232</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>232</v>
@@ -4935,19 +5011,19 @@
         <v>236</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>246</v>
@@ -4956,39 +5032,39 @@
         <v>273</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="T3" s="33" t="s">
         <v>226</v>
       </c>
       <c r="U3" s="34" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="V3" s="34" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="W3" s="34" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="X3" s="34" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="Y3" s="34" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>227</v>
@@ -5000,37 +5076,37 @@
         <v>227</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>271</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="T4" s="33" t="s">
         <v>241</v>
@@ -5039,162 +5115,162 @@
         <v>74</v>
       </c>
       <c r="V4" s="34" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="W4" s="34" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="X4" s="34" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="Y4" s="34" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="H5" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="T5" s="33" t="s">
         <v>561</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>562</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>563</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>564</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>565</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>566</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>567</v>
-      </c>
-      <c r="T5" s="33" t="s">
-        <v>549</v>
       </c>
       <c r="U5" s="34" t="s">
         <v>74</v>
       </c>
       <c r="V5" s="34" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="W5" s="34" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="X5" s="34" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="Y5" s="34" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="8" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>271</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="M6" s="8" t="s">
         <v>231</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="8" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="8" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J9" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="T9" s="35" t="s">
         <v>242</v>
       </c>
       <c r="U9" s="8" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J10" s="8" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="T10" s="35" t="s">
         <v>232</v>
       </c>
       <c r="U10" s="8" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J11" s="8" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="M11" s="8" t="s">
         <v>139</v>
@@ -5203,56 +5279,56 @@
         <v>227</v>
       </c>
       <c r="U11" s="8" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J12" s="8" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="M12" s="8" t="s">
         <v>190</v>
       </c>
       <c r="T12" s="35" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="U12" s="8" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M13" s="8" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="T13" s="35" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="U13" s="8" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M14" s="8" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M15" s="8" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M16" s="8" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="T16" s="5" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="U16" s="36" t="n">
         <v>0.95</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5262,16 +5338,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M18" s="8" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="U18" s="37" t="n">
         <v>45777</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>
@@ -5364,8 +5440,8 @@
         <v>56</v>
       </c>
       <c r="C11" s="15" t="str">
-        <f aca="false">COUNTIF('Browser &amp; desktop'!$N$2:$N$22,"Yes")&amp;" of "&amp;COUNTIF('Browser &amp; desktop'!$A$2:$A$22,"?*")</f>
-        <v>0 of 10</v>
+        <f aca="false">COUNTIF('Browser &amp; desktop'!$N$2:$N$23,"Yes")&amp;" of "&amp;COUNTIF('Browser &amp; desktop'!$A$2:$A$23,"?*")</f>
+        <v>0 of 11</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6803,7 +6879,7 @@
       </c>
       <c r="W2" s="25" t="n">
         <f aca="true">IF(OR(T2="",LEFT(O2,6)="Closed"),"",TODAY()-T2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" s="25" t="str">
         <f aca="true">IF(OR(S2="",LEFT(O2,6)="Closed"),"",IF(TODAY()&gt;S2,"Overdue",""))</f>
@@ -6878,7 +6954,7 @@
       </c>
       <c r="W3" s="25" t="n">
         <f aca="true">IF(OR(T3="",LEFT(O3,6)="Closed"),"",TODAY()-T3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" s="25" t="str">
         <f aca="true">IF(OR(S3="",LEFT(O3,6)="Closed"),"",IF(TODAY()&gt;S3,"Overdue",""))</f>
@@ -19759,7 +19835,7 @@
     <tabColor rgb="FF1C7293"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -19945,7 +20021,7 @@
         <v>301</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="D6" s="20"/>
       <c r="E6" s="20"/>
@@ -19968,12 +20044,14 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="C7" s="20"/>
+        <v>304</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>290</v>
+      </c>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
       <c r="F7" s="20"/>
@@ -19995,14 +20073,12 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>290</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="C8" s="20"/>
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
       <c r="F8" s="20"/>
@@ -20024,13 +20100,13 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
@@ -20058,7 +20134,9 @@
       <c r="B10" s="20" t="s">
         <v>309</v>
       </c>
-      <c r="C10" s="20"/>
+      <c r="C10" s="20" t="s">
+        <v>310</v>
+      </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20"/>
@@ -20076,20 +20154,16 @@
         <f aca="false">IF(A10="","",IF(AND(E10="Y",F10="Y",G10="Y",H10="Y",OR(I10="Y",I10="N/A"),J10="Pass",N(M10)&gt;=Lists!$U$16),"Yes","No"))</f>
         <v>No</v>
       </c>
-      <c r="O10" s="20" t="s">
-        <v>310</v>
-      </c>
+      <c r="O10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
         <v>311</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>299</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C11" s="20"/>
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
       <c r="F11" s="20"/>
@@ -20107,12 +20181,20 @@
         <f aca="false">IF(A11="","",IF(AND(E11="Y",F11="Y",G11="Y",H11="Y",OR(I11="Y",I11="N/A"),J11="Pass",N(M11)&gt;=Lists!$U$16),"Yes","No"))</f>
         <v>No</v>
       </c>
-      <c r="O11" s="20"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
+      <c r="O11" s="20" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>302</v>
+      </c>
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
       <c r="F12" s="20"/>
@@ -20128,7 +20210,7 @@
       </c>
       <c r="N12" s="27" t="str">
         <f aca="false">IF(A12="","",IF(AND(E12="Y",F12="Y",G12="Y",H12="Y",OR(I12="Y",I12="N/A"),J12="Pass",N(M12)&gt;=Lists!$U$16),"Yes","No"))</f>
-        <v/>
+        <v>No</v>
       </c>
       <c r="O12" s="20"/>
     </row>
@@ -20362,30 +20444,53 @@
       </c>
       <c r="O22" s="20"/>
     </row>
-    <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="30" t="s">
-        <v>312</v>
-      </c>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="29" t="str">
+        <f aca="false">IF(OR(K23="",K23=0),"",L23/K23)</f>
+        <v/>
+      </c>
+      <c r="N23" s="27" t="str">
+        <f aca="false">IF(A23="","",IF(AND(E23="Y",F23="Y",G23="Y",H23="Y",OR(I23="Y",I23="N/A"),J23="Pass",N(M23)&gt;=Lists!$U$16),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="O23" s="20"/>
+    </row>
+    <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A25:O25"/>
   </mergeCells>
-  <conditionalFormatting sqref="N2:N22">
+  <conditionalFormatting sqref="N2:N23">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>"Yes"</formula>
     </cfRule>
@@ -20394,15 +20499,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" error="Choose a value from the list (see the Lists sheet)." errorStyle="stop" errorTitle="Not in list" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E2:H22" type="list">
+    <dataValidation allowBlank="true" error="Choose a value from the list (see the Lists sheet)." errorStyle="stop" errorTitle="Not in list" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E2:H23" type="list">
       <formula1>Lists!$F$2:$F$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Choose a value from the list (see the Lists sheet)." errorStyle="stop" errorTitle="Not in list" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I22" type="list">
+    <dataValidation allowBlank="true" error="Choose a value from the list (see the Lists sheet)." errorStyle="stop" errorTitle="Not in list" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I23" type="list">
       <formula1>Lists!$G$2:$G$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Choose a value from the list (see the Lists sheet)." errorStyle="stop" errorTitle="Not in list" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J22" type="list">
+    <dataValidation allowBlank="true" error="Choose a value from the list (see the Lists sheet)." errorStyle="stop" errorTitle="Not in list" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J23" type="list">
       <formula1>Lists!$H$2:$H$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -20447,91 +20552,91 @@
         <v>76</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E1" s="16" t="s">
         <v>277</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I1" s="24" t="s">
         <v>46</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N1" s="16" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="O1" s="16" t="s">
         <v>84</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>241</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="I2" s="25" t="str">
         <f aca="false">IF(OR(G2="",H2=""),"",IFERROR(INDEX(Lists!$U$3:$Y$5,MATCH(G2,Lists!$T$3:$T$5,0),MATCH(H2,Lists!$U$2:$Y$2,0)),"Check inputs"))</f>
         <v>P2</v>
       </c>
       <c r="J2" s="25" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L2" s="25" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="M2" s="25" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="N2" s="26" t="n">
         <v>46346</v>
@@ -20540,7 +20645,7 @@
         <v>273</v>
       </c>
       <c r="P2" s="25" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26909,66 +27014,66 @@
         <v>76</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E1" s="16" t="s">
         <v>277</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K1" s="16" t="s">
         <v>84</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="J2" s="26" t="n">
         <v>46332</v>
@@ -26977,7 +27082,7 @@
         <v>273</v>
       </c>
       <c r="L2" s="25" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29803,60 +29908,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>84</v>
       </c>
       <c r="K1" s="24" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>241</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="H2" s="26" t="n">
         <v>46322</v>
@@ -29865,11 +29970,11 @@
         <v>46346</v>
       </c>
       <c r="J2" s="25" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="K2" s="25" t="n">
         <f aca="true">IF(OR(I2="",J2="Closed",J2="Rejected"),"",I2-TODAY())</f>
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
